--- a/src/docs/excel_templates/loan_balance.xlsx
+++ b/src/docs/excel_templates/loan_balance.xlsx
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Template Columns</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Employee Code</t>
   </si>
@@ -67,7 +64,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="dd/mmm/yyyy;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,13 +78,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -537,154 +527,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1026,89 +1015,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="15.2166666666667" customWidth="1"/>
-    <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="20.5583333333333" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="16.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="16.2" customWidth="1"/>
+    <col min="2" max="2" width="16.7" customWidth="1"/>
+    <col min="3" max="3" width="10.8" customWidth="1"/>
+    <col min="4" max="4" width="21.8" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="23.1" customWidth="1"/>
+    <col min="7" max="7" width="19.6" customWidth="1"/>
+    <col min="8" max="8" width="8.1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="2" spans="3:5">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="3:5">
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="3:5">
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="3:5">
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="3:5">
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="3:5">
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="3:5">
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="3:5">
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="3:5">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
